--- a/tests/data/sample.xlsx
+++ b/tests/data/sample.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CustomSheet" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BMI" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="number" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BMI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="アニメ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,30 +415,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>col1</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>col2</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>val1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>val2</t>
+          <t>AE3803</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AA5100</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NT4201</t>
         </is>
       </c>
     </row>
@@ -453,29 +457,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>身長(cm)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>体重(kg)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>BMI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>charlie</t>
-        </is>
+      <c r="A2" t="n">
+        <v>158</v>
       </c>
       <c r="B2" t="n">
-        <v>95</v>
+        <v>45</v>
+      </c>
+      <c r="C2">
+        <f>B2/((A2/100)^2)</f>
+        <v>18.02595738</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>153</v>
+      </c>
+      <c r="B3" t="n">
+        <v>38</v>
+      </c>
+      <c r="C3">
+        <f>B3/((A3/100)^2)</f>
+        <v>16.23298731</v>
       </c>
     </row>
   </sheetData>
@@ -489,48 +512,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>身長(cm)</t>
+          <t>はたらく細胞</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>体重(kg)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>BMI</t>
+          <t>2018年7月8日</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>158</v>
-      </c>
-      <c r="B2" t="n">
-        <v>45</v>
-      </c>
-      <c r="C2">
-        <f>B2/((A2/100)^2)</f>
-        <v>18.02595738</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>153</v>
-      </c>
-      <c r="B3" t="n">
-        <v>38</v>
-      </c>
-      <c r="C3">
-        <f>B3/((A3/100)^2)</f>
-        <v>16.23298731</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>化物語</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2009年7月3日</t>
+        </is>
       </c>
     </row>
   </sheetData>
